--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/Stat2430/data-viz-course/data-viz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/S2430/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F77433C-6C1B-294E-9C7F-8A052DC90F05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65092E5-E41A-1B42-8C73-47574A21AB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31220" yWindow="-80" windowWidth="28800" windowHeight="17500" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="211">
   <si>
     <t>Date</t>
   </si>
@@ -156,12 +156,6 @@
     <t>Graphics output</t>
   </si>
   <si>
-    <t>Project proposal due</t>
-  </si>
-  <si>
-    <t>Project report due</t>
-  </si>
-  <si>
     <t>#task-b3</t>
   </si>
   <si>
@@ -414,9 +408,6 @@
     <t>Assignment 1</t>
   </si>
   <si>
-    <t>Report</t>
-  </si>
-  <si>
     <t>Assignment 2</t>
   </si>
   <si>
@@ -444,9 +435,6 @@
     <t>#assignment-5</t>
   </si>
   <si>
-    <t>#written-report</t>
-  </si>
-  <si>
     <t>#proposal</t>
   </si>
   <si>
@@ -564,9 +552,6 @@
     <t>08-gg-practice</t>
   </si>
   <si>
-    <t>Practice with the grammar of graphics</t>
-  </si>
-  <si>
     <t>09-summarize</t>
   </si>
   <si>
@@ -636,9 +621,6 @@
     <t>ggplot intro</t>
   </si>
   <si>
-    <t>Oral presentation due 1 day before final exam</t>
-  </si>
-  <si>
     <t>Practice summarizing data</t>
   </si>
   <si>
@@ -666,10 +648,25 @@
     <t>35-step-by-step.html</t>
   </si>
   <si>
-    <t>Snow day</t>
-  </si>
-  <si>
     <t>36-presentation-recording.html</t>
+  </si>
+  <si>
+    <t>Oral presentation due</t>
+  </si>
+  <si>
+    <t>Mid-term test</t>
+  </si>
+  <si>
+    <t>Assignment 0 due</t>
+  </si>
+  <si>
+    <t>Assignment 0</t>
+  </si>
+  <si>
+    <t>#assignment-0</t>
+  </si>
+  <si>
+    <t>Project proposal discussions</t>
   </si>
 </sst>
 </file>
@@ -750,9 +747,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -790,7 +787,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -896,7 +893,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1038,7 +1035,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1068,19 +1065,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>11</v>
@@ -1089,10 +1086,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1100,11 +1097,11 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3">
-        <f>DATEVALUE("2024-01-07")+B2+(A2-1)*7</f>
-        <v>45300</v>
+        <f>DATEVALUE("2026-01-04")+B2+(A2-1)*7</f>
+        <v>46030</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
@@ -1119,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1129,17 +1126,17 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C50" si="0">DATEVALUE("2024-01-07")+B3+(A3-1)*7</f>
-        <v>45300</v>
+        <f t="shared" ref="C3:C50" si="0">DATEVALUE("2026-01-04")+B3+(A3-1)*7</f>
+        <v>46030</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -1154,33 +1151,33 @@
         <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="0"/>
-        <v>45302</v>
+        <v>46035</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -1189,46 +1186,46 @@
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="0"/>
-        <v>45302</v>
+        <v>46035</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1236,17 +1233,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="0"/>
-        <v>45307</v>
+        <v>46037</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -1261,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1271,23 +1268,23 @@
         <v>2</v>
       </c>
       <c r="B7" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="0"/>
-        <v>45307</v>
+        <v>46037</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>20</v>
@@ -1296,13 +1293,13 @@
         <v>10</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1310,39 +1307,27 @@
         <v>2</v>
       </c>
       <c r="B8" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
-        <v>45309</v>
+        <v>46038</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="2">
-        <v>6</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>174</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -1353,63 +1338,67 @@
       </c>
       <c r="C9" s="3">
         <f t="shared" si="0"/>
-        <v>45314</v>
+        <v>46042</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F9" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>196</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>3</v>
       </c>
       <c r="B10" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="0"/>
-        <v>45314</v>
+        <v>46044</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F10" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1419,54 +1408,66 @@
         <v>3</v>
       </c>
       <c r="B11" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="0"/>
-        <v>45317</v>
+        <v>46044</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>3</v>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="0"/>
-        <v>45316</v>
+        <v>46045</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>175</v>
-      </c>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -1477,19 +1478,19 @@
       </c>
       <c r="C13" s="3">
         <f t="shared" si="0"/>
-        <v>45321</v>
+        <v>46049</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F13" s="2">
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>21</v>
@@ -1498,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1510,16 +1511,16 @@
       </c>
       <c r="C14" s="3">
         <f t="shared" si="0"/>
-        <v>45323</v>
+        <v>46051</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1531,19 +1532,19 @@
       </c>
       <c r="C15" s="3">
         <f t="shared" si="0"/>
-        <v>45323</v>
+        <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>22</v>
@@ -1552,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1564,28 +1565,28 @@
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
-        <v>45328</v>
+        <v>46056</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F16" s="2">
         <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1599,19 +1600,19 @@
       </c>
       <c r="C17" s="3">
         <f t="shared" si="0"/>
-        <v>45328</v>
+        <v>46056</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F17" s="2">
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>23</v>
@@ -1620,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1634,18 +1635,18 @@
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
-        <v>45331</v>
+        <v>46059</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -1661,19 +1662,19 @@
       </c>
       <c r="C19" s="3">
         <f t="shared" si="0"/>
-        <v>45330</v>
+        <v>46058</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F19" s="2">
         <v>13</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>24</v>
@@ -1682,13 +1683,13 @@
         <v>10</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -1700,28 +1701,28 @@
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
-        <v>45330</v>
+        <v>46058</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F20" s="2">
         <v>14</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
@@ -1735,34 +1736,34 @@
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
-        <v>45335</v>
+        <v>46063</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F21" s="2">
         <v>15</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -1774,13 +1775,13 @@
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
-        <v>45335</v>
+        <v>46063</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" s="2">
         <v>16</v>
@@ -1789,13 +1790,13 @@
         <v>30</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
@@ -1809,28 +1810,28 @@
       </c>
       <c r="C23" s="3">
         <f t="shared" si="0"/>
-        <v>45337</v>
+        <v>46065</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2">
         <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
@@ -1844,10 +1845,10 @@
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
-        <v>45341</v>
+        <v>46069</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
@@ -1860,25 +1861,25 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="0"/>
-        <v>45337</v>
+        <v>46059</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -1890,33 +1891,21 @@
         <v>8</v>
       </c>
       <c r="B26" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="0"/>
-        <v>45349</v>
+        <v>46079</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="2">
-        <v>18</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>158</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
@@ -1925,25 +1914,33 @@
         <v>8</v>
       </c>
       <c r="B27" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="0"/>
-        <v>45352</v>
+        <v>46077</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="2">
+        <v>18</v>
+      </c>
       <c r="G27" s="2" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
@@ -1952,33 +1949,25 @@
         <v>8</v>
       </c>
       <c r="B28" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="0"/>
-        <v>45351</v>
+        <v>46076</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F28" s="2">
-        <v>19</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>178</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
@@ -1987,233 +1976,225 @@
         <v>8</v>
       </c>
       <c r="B29" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="0"/>
-        <v>45351</v>
+        <v>46077</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F29" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B30" s="2">
         <v>2</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" si="0"/>
-        <v>45356</v>
+        <v>46077</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2">
-        <v>21</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>53</v>
+      </c>
       <c r="I30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" si="0"/>
-        <v>45358</v>
+        <v>46091</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F31" s="2">
-        <v>22</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>63</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
       <c r="I31" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B32" s="2">
         <v>4</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" si="0"/>
-        <v>45358</v>
+        <v>46093</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F32" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2">
         <v>4</v>
       </c>
       <c r="C33" s="3">
         <f t="shared" si="0"/>
-        <v>45358</v>
+        <v>46093</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F33" s="2">
+        <v>23</v>
+      </c>
       <c r="G33" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2">
         <v>2</v>
       </c>
       <c r="C34" s="3">
         <f t="shared" si="0"/>
-        <v>45363</v>
+        <v>46084</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F34" s="2">
-        <v>24</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="K34" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" si="0"/>
-        <v>45366</v>
+        <v>46086</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="4"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
@@ -2221,63 +2202,67 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B36" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36" s="3">
         <f t="shared" si="0"/>
-        <v>45365</v>
+        <v>46098</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F36" s="2">
-        <v>25</v>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="I36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B37" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="0"/>
-        <v>45365</v>
+        <v>46101</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="2">
-        <v>26</v>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>160</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
@@ -2286,39 +2271,31 @@
         <v>11</v>
       </c>
       <c r="B38" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" s="3">
         <f t="shared" si="0"/>
-        <v>45370</v>
+        <v>46100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2">
-        <v>27</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
       <c r="I38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
@@ -2329,300 +2306,304 @@
       </c>
       <c r="C39" s="3">
         <f t="shared" si="0"/>
-        <v>45372</v>
+        <v>46100</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2">
-        <v>28</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
       <c r="I39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40" s="3">
         <f t="shared" si="0"/>
-        <v>45372</v>
+        <v>46105</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F40" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
+        <v>157</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>12</v>
       </c>
       <c r="B41" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="0"/>
-        <v>45377</v>
+        <v>46107</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F41" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B42" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C42" s="3">
         <f t="shared" si="0"/>
-        <v>45383</v>
+        <v>46107</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F42" s="2">
+        <v>29</v>
+      </c>
       <c r="G42" s="2" t="s">
-        <v>130</v>
+        <v>82</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43" s="3">
         <f t="shared" si="0"/>
-        <v>45379</v>
+        <v>46112</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F43" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>204</v>
+        <v>56</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B44" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="0"/>
-        <v>45379</v>
+        <v>46111</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="2">
-        <v>32</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>38</v>
+        <v>127</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>13</v>
       </c>
       <c r="B45" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="0"/>
-        <v>45384</v>
+        <v>46114</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>206</v>
+        <v>115</v>
       </c>
       <c r="F45" s="2">
-        <v>33</v>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="I45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>13</v>
       </c>
       <c r="B46" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="0"/>
-        <v>45384</v>
+        <v>46114</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F46" s="2">
-        <v>34</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="I46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="0"/>
-        <v>45386</v>
+        <v>46119</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="F47" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -2630,33 +2611,45 @@
         <v>10</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="0"/>
-        <v>45386</v>
+        <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F48" s="2">
+        <v>34</v>
+      </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
@@ -2667,51 +2660,56 @@
       </c>
       <c r="C49" s="3">
         <f t="shared" si="0"/>
-        <v>45391</v>
+        <v>46119</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F49" s="2">
+        <v>35</v>
+      </c>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B50" s="2">
         <v>2</v>
       </c>
-      <c r="C50" s="1">
-        <f t="shared" si="0"/>
-        <v>45398</v>
+      <c r="C50" s="3">
+        <f t="shared" si="0"/>
+        <v>46119</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L48">
-    <sortCondition ref="A2:A48"/>
-    <sortCondition ref="B2:B48"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L49">
+    <sortCondition ref="A2:A49"/>
+    <sortCondition ref="B2:B49"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/S2430/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A65092E5-E41A-1B42-8C73-47574A21AB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0BBC44-86FA-B949-B917-ED4DBFCB50BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -399,9 +399,6 @@
     <t>Team Planning</t>
   </si>
   <si>
-    <t>#task-planning</t>
-  </si>
-  <si>
     <t>Proposal</t>
   </si>
   <si>
@@ -667,6 +664,9 @@
   </si>
   <si>
     <t>Project proposal discussions</t>
+  </si>
+  <si>
+    <t>#team-creation</t>
   </si>
 </sst>
 </file>
@@ -1074,10 +1074,10 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>11</v>
@@ -1086,10 +1086,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1116,7 +1116,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" ref="C3:C50" si="0">DATEVALUE("2026-01-04")+B3+(A3-1)*7</f>
+        <f>DATEVALUE("2026-01-04")+B3+(A3-1)*7</f>
         <v>46030</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B4+(A4-1)*7</f>
         <v>46035</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1177,7 +1177,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -1186,7 +1186,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1199,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B5+(A5-1)*7</f>
         <v>46035</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1218,14 +1218,14 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1236,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B6+(A6-1)*7</f>
         <v>46037</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1258,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1271,7 +1271,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B7+(A7-1)*7</f>
         <v>46037</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1284,7 +1284,7 @@
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>20</v>
@@ -1293,13 +1293,13 @@
         <v>10</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1310,19 +1310,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B8+(A8-1)*7</f>
         <v>46038</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1337,7 +1337,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B9+(A9-1)*7</f>
         <v>46042</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1350,22 +1350,22 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1376,7 +1376,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B10+(A10-1)*7</f>
         <v>46044</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1389,7 +1389,7 @@
         <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>40</v>
@@ -1398,7 +1398,7 @@
         <v>10</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1411,7 +1411,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B11+(A11-1)*7</f>
         <v>46044</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1424,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>41</v>
@@ -1433,13 +1433,13 @@
         <v>10</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1450,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B12+(A12-1)*7</f>
         <v>46045</v>
       </c>
       <c r="D12" s="2" t="s">
@@ -1459,10 +1459,10 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1477,7 +1477,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B13+(A13-1)*7</f>
         <v>46049</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1510,17 +1510,17 @@
         <v>4</v>
       </c>
       <c r="C14" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B14+(A14-1)*7</f>
         <v>46051</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B15+(A15-1)*7</f>
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1564,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B16+(A16-1)*7</f>
         <v>46056</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -1577,7 +1577,7 @@
         <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>43</v>
@@ -1586,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
@@ -1599,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B17+(A17-1)*7</f>
         <v>46056</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -1621,7 +1621,7 @@
         <v>10</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1631,27 +1631,39 @@
         <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" si="0"/>
-        <v>46059</v>
+        <f>DATEVALUE("2026-01-04")+B18+(A18-1)*7</f>
+        <v>46058</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="2">
+        <v>13</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -1661,23 +1673,23 @@
         <v>4</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B19+(A19-1)*7</f>
         <v>46058</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F19" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>10</v>
@@ -1685,86 +1697,62 @@
       <c r="J19" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>197</v>
-      </c>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" si="0"/>
-        <v>46058</v>
+        <f>DATEVALUE("2026-01-04")+B20+(A20-1)*7</f>
+        <v>46059</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="F20" s="2">
-        <v>14</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
       <c r="G20" s="2" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3">
-        <f t="shared" si="0"/>
-        <v>46063</v>
+        <f>DATEVALUE("2026-01-04")+B21+(A21-1)*7</f>
+        <v>46059</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F21" s="2">
-        <v>15</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
@@ -1774,113 +1762,125 @@
         <v>2</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B22+(A22-1)*7</f>
         <v>46063</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>6</v>
       </c>
       <c r="B23" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" si="0"/>
-        <v>46065</v>
+        <f>DATEVALUE("2026-01-04")+B23+(A23-1)*7</f>
+        <v>46063</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F23" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" si="0"/>
-        <v>46069</v>
+        <f>DATEVALUE("2026-01-04")+B24+(A24-1)*7</f>
+        <v>46065</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="2">
+        <v>17</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B25" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" si="0"/>
-        <v>46059</v>
+        <f>DATEVALUE("2026-01-04")+B25+(A25-1)*7</f>
+        <v>46069</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>188</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1891,19 +1891,23 @@
         <v>8</v>
       </c>
       <c r="B26" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" si="0"/>
-        <v>46079</v>
+        <f>DATEVALUE("2026-01-04")+B26+(A26-1)*7</f>
+        <v>46076</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>206</v>
+        <v>72</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1917,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B27+(A27-1)*7</f>
         <v>46077</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -1930,7 +1934,7 @@
         <v>18</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>51</v>
@@ -1939,7 +1943,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
@@ -1949,25 +1953,33 @@
         <v>8</v>
       </c>
       <c r="B28" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" si="0"/>
-        <v>46076</v>
+        <f>DATEVALUE("2026-01-04")+B28+(A28-1)*7</f>
+        <v>46077</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
+        <v>54</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F28" s="2">
+        <v>19</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
@@ -1979,23 +1991,23 @@
         <v>2</v>
       </c>
       <c r="C29" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B29+(A29-1)*7</f>
         <v>46077</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F29" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>198</v>
+        <v>80</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>10</v>
@@ -2003,115 +2015,83 @@
       <c r="J29" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
+      <c r="K29" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>8</v>
       </c>
       <c r="B30" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30" s="3">
-        <f t="shared" si="0"/>
-        <v>46077</v>
+        <f>DATEVALUE("2026-01-04")+B30+(A30-1)*7</f>
+        <v>46079</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="2">
-        <v>20</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>176</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2">
         <v>2</v>
       </c>
       <c r="C31" s="3">
-        <f t="shared" si="0"/>
-        <v>46091</v>
+        <f>DATEVALUE("2026-01-04")+B31+(A31-1)*7</f>
+        <v>46084</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F31" s="2">
-        <v>21</v>
-      </c>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2">
         <v>4</v>
       </c>
       <c r="C32" s="3">
-        <f t="shared" si="0"/>
-        <v>46093</v>
+        <f>DATEVALUE("2026-01-04")+B32+(A32-1)*7</f>
+        <v>46086</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F32" s="2">
-        <v>22</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>178</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
@@ -2120,83 +2100,103 @@
         <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="3">
-        <f t="shared" si="0"/>
-        <v>46093</v>
+        <f>DATEVALUE("2026-01-04")+B33+(A33-1)*7</f>
+        <v>46091</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2">
-        <v>23</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>62</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
       <c r="I33" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" s="3">
-        <f t="shared" si="0"/>
-        <v>46084</v>
+        <f>DATEVALUE("2026-01-04")+B34+(A34-1)*7</f>
+        <v>46093</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F34" s="2">
+        <v>22</v>
+      </c>
       <c r="G34" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B35" s="2">
         <v>4</v>
       </c>
       <c r="C35" s="3">
-        <f t="shared" si="0"/>
-        <v>46086</v>
+        <f>DATEVALUE("2026-01-04")+B35+(A35-1)*7</f>
+        <v>46093</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="2">
+        <v>23</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
@@ -2208,7 +2208,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B36+(A36-1)*7</f>
         <v>46098</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -2221,22 +2221,22 @@
         <v>24</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -2244,25 +2244,29 @@
         <v>11</v>
       </c>
       <c r="B37" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37" s="3">
-        <f t="shared" si="0"/>
-        <v>46101</v>
+        <f>DATEVALUE("2026-01-04")+B37+(A37-1)*7</f>
+        <v>46100</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F37" s="2">
+        <v>25</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
@@ -2274,17 +2278,17 @@
         <v>4</v>
       </c>
       <c r="C38" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B38+(A38-1)*7</f>
         <v>46100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F38" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -2302,29 +2306,25 @@
         <v>11</v>
       </c>
       <c r="B39" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" s="3">
-        <f t="shared" si="0"/>
-        <v>46100</v>
+        <f>DATEVALUE("2026-01-04")+B39+(A39-1)*7</f>
+        <v>46101</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F39" s="2">
-        <v>26</v>
-      </c>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>156</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
@@ -2336,7 +2336,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B40+(A40-1)*7</f>
         <v>46105</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -2349,7 +2349,7 @@
         <v>27</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>63</v>
@@ -2358,13 +2358,13 @@
         <v>10</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -2375,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B41+(A41-1)*7</f>
         <v>46107</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -2397,13 +2397,13 @@
         <v>10</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -2414,7 +2414,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B42+(A42-1)*7</f>
         <v>46107</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -2436,76 +2436,76 @@
         <v>10</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="3">
-        <f t="shared" si="0"/>
-        <v>46112</v>
+        <f>DATEVALUE("2026-01-04")+B43+(A43-1)*7</f>
+        <v>46118</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F43" s="2">
-        <v>30</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>13</v>
       </c>
       <c r="B44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" s="3">
-        <f t="shared" si="0"/>
-        <v>46111</v>
+        <f>DATEVALUE("2026-01-04")+B44+(A44-1)*7</f>
+        <v>46112</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F44" s="2">
+        <v>30</v>
+      </c>
       <c r="G44" s="2" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
@@ -2515,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B45+(A45-1)*7</f>
         <v>46114</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -2528,7 +2528,7 @@
         <v>31</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>66</v>
@@ -2537,13 +2537,13 @@
         <v>10</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -2554,7 +2554,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B46+(A46-1)*7</f>
         <v>46114</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -2576,13 +2576,13 @@
         <v>10</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
@@ -2593,14 +2593,14 @@
         <v>2</v>
       </c>
       <c r="C47" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B47+(A47-1)*7</f>
         <v>46119</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="F47" s="2">
         <v>33</v>
@@ -2611,7 +2611,7 @@
         <v>10</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
@@ -2624,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B48+(A48-1)*7</f>
         <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -2642,13 +2642,13 @@
         <v>10</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -2659,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="C49" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B49+(A49-1)*7</f>
         <v>46119</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -2677,7 +2677,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
@@ -2690,23 +2690,23 @@
         <v>2</v>
       </c>
       <c r="C50" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B50+(A50-1)*7</f>
         <v>46119</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L49">
-    <sortCondition ref="A2:A49"/>
-    <sortCondition ref="B2:B49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L50">
+    <sortCondition ref="A2:A50"/>
+    <sortCondition ref="B2:B50"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/S2430/data-viz-course/data-viz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0BBC44-86FA-B949-B917-ED4DBFCB50BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BAC08F-9089-8D4F-B61E-1415553D359A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19860" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1100,7 +1100,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <f>DATEVALUE("2026-01-04")+B2+(A2-1)*7</f>
+        <f t="shared" ref="C2:C33" si="0">DATEVALUE("2026-01-04")+B2+(A2-1)*7</f>
         <v>46030</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1129,7 +1129,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="3">
-        <f>DATEVALUE("2026-01-04")+B3+(A3-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46030</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <f>DATEVALUE("2026-01-04")+B4+(A4-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46035</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1199,7 +1199,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3">
-        <f>DATEVALUE("2026-01-04")+B5+(A5-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46035</v>
       </c>
       <c r="D5" s="2" t="s">
@@ -1236,7 +1236,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3">
-        <f>DATEVALUE("2026-01-04")+B6+(A6-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46037</v>
       </c>
       <c r="D6" s="2" t="s">
@@ -1271,7 +1271,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="3">
-        <f>DATEVALUE("2026-01-04")+B7+(A7-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46037</v>
       </c>
       <c r="D7" s="2" t="s">
@@ -1310,7 +1310,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <f>DATEVALUE("2026-01-04")+B8+(A8-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46038</v>
       </c>
       <c r="D8" s="2" t="s">
@@ -1337,7 +1337,7 @@
         <v>2</v>
       </c>
       <c r="C9" s="3">
-        <f>DATEVALUE("2026-01-04")+B9+(A9-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46042</v>
       </c>
       <c r="D9" s="2" t="s">
@@ -1376,7 +1376,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="3">
-        <f>DATEVALUE("2026-01-04")+B10+(A10-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46044</v>
       </c>
       <c r="D10" s="2" t="s">
@@ -1411,7 +1411,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="3">
-        <f>DATEVALUE("2026-01-04")+B11+(A11-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46044</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1444,14 +1444,14 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2">
         <v>5</v>
       </c>
       <c r="C12" s="3">
-        <f>DATEVALUE("2026-01-04")+B12+(A12-1)*7</f>
-        <v>46045</v>
+        <f t="shared" si="0"/>
+        <v>46052</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>70</v>
@@ -1477,7 +1477,7 @@
         <v>2</v>
       </c>
       <c r="C13" s="3">
-        <f>DATEVALUE("2026-01-04")+B13+(A13-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46049</v>
       </c>
       <c r="D13" s="2" t="s">
@@ -1510,7 +1510,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="3">
-        <f>DATEVALUE("2026-01-04")+B14+(A14-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46051</v>
       </c>
       <c r="D14" s="2" t="s">
@@ -1531,7 +1531,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="3">
-        <f>DATEVALUE("2026-01-04")+B15+(A15-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -1564,7 +1564,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="3">
-        <f>DATEVALUE("2026-01-04")+B16+(A16-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46056</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -1599,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="C17" s="3">
-        <f>DATEVALUE("2026-01-04")+B17+(A17-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46056</v>
       </c>
       <c r="D17" s="2" t="s">
@@ -1634,7 +1634,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="3">
-        <f>DATEVALUE("2026-01-04")+B18+(A18-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46058</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -1673,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="3">
-        <f>DATEVALUE("2026-01-04")+B19+(A19-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46058</v>
       </c>
       <c r="D19" s="2" t="s">
@@ -1708,7 +1708,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="3">
-        <f>DATEVALUE("2026-01-04")+B20+(A20-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46059</v>
       </c>
       <c r="D20" s="2" t="s">
@@ -1735,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="C21" s="3">
-        <f>DATEVALUE("2026-01-04")+B21+(A21-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46059</v>
       </c>
       <c r="D21" s="2" t="s">
@@ -1762,7 +1762,7 @@
         <v>2</v>
       </c>
       <c r="C22" s="3">
-        <f>DATEVALUE("2026-01-04")+B22+(A22-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46063</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -1801,7 +1801,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="3">
-        <f>DATEVALUE("2026-01-04")+B23+(A23-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46063</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -1836,7 +1836,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <f>DATEVALUE("2026-01-04")+B24+(A24-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46065</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -1871,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="3">
-        <f>DATEVALUE("2026-01-04")+B25+(A25-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46069</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -1894,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="3">
-        <f>DATEVALUE("2026-01-04")+B26+(A26-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46076</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -1921,7 +1921,7 @@
         <v>2</v>
       </c>
       <c r="C27" s="3">
-        <f>DATEVALUE("2026-01-04")+B27+(A27-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46077</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -1956,7 +1956,7 @@
         <v>2</v>
       </c>
       <c r="C28" s="3">
-        <f>DATEVALUE("2026-01-04")+B28+(A28-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46077</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -1991,7 +1991,7 @@
         <v>2</v>
       </c>
       <c r="C29" s="3">
-        <f>DATEVALUE("2026-01-04")+B29+(A29-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46077</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -2030,7 +2030,7 @@
         <v>4</v>
       </c>
       <c r="C30" s="3">
-        <f>DATEVALUE("2026-01-04")+B30+(A30-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46079</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -2053,7 +2053,7 @@
         <v>2</v>
       </c>
       <c r="C31" s="3">
-        <f>DATEVALUE("2026-01-04")+B31+(A31-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46084</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -2080,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="3">
-        <f>DATEVALUE("2026-01-04")+B32+(A32-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46086</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -2103,7 +2103,7 @@
         <v>2</v>
       </c>
       <c r="C33" s="3">
-        <f>DATEVALUE("2026-01-04")+B33+(A33-1)*7</f>
+        <f t="shared" si="0"/>
         <v>46091</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="3">
-        <f>DATEVALUE("2026-01-04")+B34+(A34-1)*7</f>
+        <f t="shared" ref="C34:C65" si="1">DATEVALUE("2026-01-04")+B34+(A34-1)*7</f>
         <v>46093</v>
       </c>
       <c r="D34" s="2" t="s">
@@ -2173,7 +2173,7 @@
         <v>4</v>
       </c>
       <c r="C35" s="3">
-        <f>DATEVALUE("2026-01-04")+B35+(A35-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46093</v>
       </c>
       <c r="D35" s="2" t="s">
@@ -2208,7 +2208,7 @@
         <v>2</v>
       </c>
       <c r="C36" s="3">
-        <f>DATEVALUE("2026-01-04")+B36+(A36-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46098</v>
       </c>
       <c r="D36" s="2" t="s">
@@ -2247,7 +2247,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="3">
-        <f>DATEVALUE("2026-01-04")+B37+(A37-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46100</v>
       </c>
       <c r="D37" s="2" t="s">
@@ -2278,7 +2278,7 @@
         <v>4</v>
       </c>
       <c r="C38" s="3">
-        <f>DATEVALUE("2026-01-04")+B38+(A38-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46100</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -2309,7 +2309,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="3">
-        <f>DATEVALUE("2026-01-04")+B39+(A39-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46101</v>
       </c>
       <c r="D39" s="2" t="s">
@@ -2336,7 +2336,7 @@
         <v>2</v>
       </c>
       <c r="C40" s="3">
-        <f>DATEVALUE("2026-01-04")+B40+(A40-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46105</v>
       </c>
       <c r="D40" s="2" t="s">
@@ -2375,7 +2375,7 @@
         <v>4</v>
       </c>
       <c r="C41" s="3">
-        <f>DATEVALUE("2026-01-04")+B41+(A41-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46107</v>
       </c>
       <c r="D41" s="2" t="s">
@@ -2414,7 +2414,7 @@
         <v>4</v>
       </c>
       <c r="C42" s="3">
-        <f>DATEVALUE("2026-01-04")+B42+(A42-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46107</v>
       </c>
       <c r="D42" s="2" t="s">
@@ -2449,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="3">
-        <f>DATEVALUE("2026-01-04")+B43+(A43-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46118</v>
       </c>
       <c r="D43" s="2" t="s">
@@ -2476,7 +2476,7 @@
         <v>2</v>
       </c>
       <c r="C44" s="3">
-        <f>DATEVALUE("2026-01-04")+B44+(A44-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46112</v>
       </c>
       <c r="D44" s="2" t="s">
@@ -2515,7 +2515,7 @@
         <v>4</v>
       </c>
       <c r="C45" s="3">
-        <f>DATEVALUE("2026-01-04")+B45+(A45-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46114</v>
       </c>
       <c r="D45" s="2" t="s">
@@ -2554,7 +2554,7 @@
         <v>4</v>
       </c>
       <c r="C46" s="3">
-        <f>DATEVALUE("2026-01-04")+B46+(A46-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46114</v>
       </c>
       <c r="D46" s="2" t="s">
@@ -2593,7 +2593,7 @@
         <v>2</v>
       </c>
       <c r="C47" s="3">
-        <f>DATEVALUE("2026-01-04")+B47+(A47-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46119</v>
       </c>
       <c r="D47" s="2" t="s">
@@ -2624,7 +2624,7 @@
         <v>2</v>
       </c>
       <c r="C48" s="3">
-        <f>DATEVALUE("2026-01-04")+B48+(A48-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
@@ -2659,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="C49" s="3">
-        <f>DATEVALUE("2026-01-04")+B49+(A49-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46119</v>
       </c>
       <c r="D49" s="2" t="s">
@@ -2690,7 +2690,7 @@
         <v>2</v>
       </c>
       <c r="C50" s="3">
-        <f>DATEVALUE("2026-01-04")+B50+(A50-1)*7</f>
+        <f t="shared" si="1"/>
         <v>46119</v>
       </c>
       <c r="D50" s="2" t="s">

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BAC08F-9089-8D4F-B61E-1415553D359A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED742CC-3759-B546-8E23-C7CF4CECE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="212">
   <si>
     <t>Date</t>
   </si>
@@ -72,9 +72,6 @@
     <t>slides</t>
   </si>
   <si>
-    <t>#task-1</t>
-  </si>
-  <si>
     <t>#task-b1</t>
   </si>
   <si>
@@ -667,6 +664,12 @@
   </si>
   <si>
     <t>#team-creation</t>
+  </si>
+  <si>
+    <t>Using AI to learn</t>
+  </si>
+  <si>
+    <t>lessons/106b-using-LLM-to-learn.html</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1046,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5054E2AF-B146-EF4C-9336-1C427A68EF7D}">
-  <dimension ref="A1:L50"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -1065,19 +1068,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>11</v>
@@ -1086,10 +1089,10 @@
         <v>9</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1100,7 +1103,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3">
-        <f t="shared" ref="C2:C33" si="0">DATEVALUE("2026-01-04")+B2+(A2-1)*7</f>
+        <f t="shared" ref="C2:C34" si="0">DATEVALUE("2026-01-04")+B2+(A2-1)*7</f>
         <v>46030</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1116,7 +1119,7 @@
         <v>10</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1136,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -1145,13 +1148,13 @@
         <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>12</v>
+        <v>207</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1171,22 +1174,22 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1206,26 +1209,26 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -1243,7 +1246,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -1252,13 +1255,13 @@
         <v>8</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1275,31 +1278,31 @@
         <v>46037</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1314,15 +1317,15 @@
         <v>46038</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1341,31 +1344,31 @@
         <v>46042</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -1380,25 +1383,25 @@
         <v>46044</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F10" s="2">
         <v>7</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -1415,31 +1418,31 @@
         <v>46044</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1454,15 +1457,15 @@
         <v>46052</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1481,25 +1484,25 @@
         <v>46049</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F13" s="2">
         <v>9</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1514,13 +1517,13 @@
         <v>46051</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1535,61 +1538,51 @@
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="2">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B16" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
-        <v>46056</v>
+        <v>46051</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="F16" s="2">
         <v>11</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -1603,25 +1596,25 @@
         <v>46056</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2">
         <v>12</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
@@ -1631,39 +1624,35 @@
         <v>5</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="0"/>
-        <v>46058</v>
+        <v>46056</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F18" s="2">
         <v>13</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>196</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
@@ -1677,53 +1666,65 @@
         <v>46058</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F19" s="2">
         <v>14</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>5</v>
       </c>
       <c r="B20" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="0"/>
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="2">
+        <v>15</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
@@ -1739,15 +1740,15 @@
         <v>46059</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>210</v>
+        <v>127</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1756,42 +1757,30 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="0"/>
-        <v>46063</v>
+        <v>46059</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="2">
-        <v>15</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>197</v>
+        <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>174</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
@@ -1805,109 +1794,121 @@
         <v>46063</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F23" s="2">
         <v>16</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>6</v>
       </c>
       <c r="B24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="0"/>
-        <v>46065</v>
+        <v>46063</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F24" s="2">
         <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="0"/>
-        <v>46069</v>
+        <v>46065</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="2">
+        <v>18</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="2">
         <v>1</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="0"/>
-        <v>46076</v>
+        <v>46069</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>72</v>
+        <v>187</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1918,33 +1919,25 @@
         <v>8</v>
       </c>
       <c r="B27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="0"/>
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" s="2">
-        <v>18</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>197</v>
+        <v>123</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>153</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
@@ -1960,25 +1953,25 @@
         <v>46077</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2">
         <v>19</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
@@ -1995,78 +1988,86 @@
         <v>46077</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2">
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>80</v>
+        <v>196</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>8</v>
       </c>
       <c r="B30" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" si="0"/>
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="2">
+        <v>21</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B31" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" si="0"/>
-        <v>46084</v>
+        <v>46079</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>132</v>
-      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -2077,19 +2078,23 @@
         <v>9</v>
       </c>
       <c r="B32" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" si="0"/>
-        <v>46086</v>
+        <v>46084</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="4"/>
+      <c r="G32" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -2097,73 +2102,61 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33" s="3">
         <f t="shared" si="0"/>
-        <v>46091</v>
+        <v>46086</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F33" s="2">
-        <v>21</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
       <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>180</v>
-      </c>
+      <c r="H33" s="4"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>10</v>
       </c>
       <c r="B34" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34" s="3">
-        <f t="shared" ref="C34:C65" si="1">DATEVALUE("2026-01-04")+B34+(A34-1)*7</f>
-        <v>46093</v>
+        <f t="shared" si="0"/>
+        <v>46091</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
       <c r="I34" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
@@ -2173,102 +2166,106 @@
         <v>4</v>
       </c>
       <c r="C35" s="3">
+        <f t="shared" ref="C35:C51" si="1">DATEVALUE("2026-01-04")+B35+(A35-1)*7</f>
+        <v>46093</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="2">
+        <v>23</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>10</v>
+      </c>
+      <c r="B36" s="2">
+        <v>4</v>
+      </c>
+      <c r="C36" s="3">
         <f t="shared" si="1"/>
         <v>46093</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F35" s="2">
-        <v>23</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="2">
-        <v>11</v>
-      </c>
-      <c r="B36" s="2">
-        <v>2</v>
-      </c>
-      <c r="C36" s="3">
-        <f t="shared" si="1"/>
-        <v>46098</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F36" s="2">
         <v>24</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>136</v>
+        <v>33</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>11</v>
       </c>
       <c r="B37" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="1"/>
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F37" s="2">
         <v>25</v>
       </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="I37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
@@ -2282,10 +2279,10 @@
         <v>46100</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F38" s="2">
         <v>26</v>
@@ -2296,7 +2293,7 @@
         <v>10</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -2306,104 +2303,96 @@
         <v>11</v>
       </c>
       <c r="B39" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="1"/>
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F39" s="2">
+        <v>27</v>
+      </c>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C40" s="3">
         <f t="shared" si="1"/>
-        <v>46105</v>
+        <v>46101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F40" s="2">
-        <v>27</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>182</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>12</v>
       </c>
       <c r="B41" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="1"/>
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F41" s="2">
         <v>28</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -2418,117 +2407,117 @@
         <v>46107</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F42" s="2">
         <v>29</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B43" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C43" s="3">
         <f t="shared" si="1"/>
-        <v>46118</v>
+        <v>46107</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F43" s="2">
+        <v>30</v>
+      </c>
       <c r="G43" s="2" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>157</v>
+      </c>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B44" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="1"/>
-        <v>46112</v>
+        <v>46118</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F44" s="2">
-        <v>30</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>185</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>13</v>
       </c>
       <c r="B45" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="1"/>
-        <v>46114</v>
+        <v>46112</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F45" s="2">
         <v>31</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>66</v>
@@ -2537,10 +2526,10 @@
         <v>10</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>184</v>
@@ -2558,63 +2547,71 @@
         <v>46114</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F46" s="2">
         <v>32</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>38</v>
+        <v>196</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="1"/>
-        <v>46119</v>
+        <v>46114</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>37</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>199</v>
+        <v>115</v>
       </c>
       <c r="F47" s="2">
         <v>33</v>
       </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="I47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
+        <v>160</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
@@ -2628,10 +2625,10 @@
         <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>39</v>
+        <v>197</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>117</v>
+        <v>198</v>
       </c>
       <c r="F48" s="2">
         <v>34</v>
@@ -2642,14 +2639,10 @@
         <v>10</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>187</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
@@ -2663,10 +2656,10 @@
         <v>46119</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F49" s="2">
         <v>35</v>
@@ -2677,10 +2670,14 @@
         <v>10</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="K49" s="2"/>
-      <c r="L49" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
@@ -2694,19 +2691,50 @@
         <v>46119</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>204</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F50" s="2">
+        <v>36</v>
+      </c>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
         <v>10</v>
       </c>
       <c r="J50" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>14</v>
+      </c>
+      <c r="B51" s="2">
+        <v>2</v>
+      </c>
+      <c r="C51" s="3">
+        <f t="shared" si="1"/>
+        <v>46119</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>203</v>
       </c>
+      <c r="I51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>202</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L50">
-    <sortCondition ref="A2:A50"/>
-    <sortCondition ref="B2:B50"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L51">
+    <sortCondition ref="A2:A51"/>
+    <sortCondition ref="B2:B51"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/S2430/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED742CC-3759-B546-8E23-C7CF4CECE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A15C36-047D-4B46-ADEE-A0D294D74262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -1307,14 +1307,14 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>205</v>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DED742CC-3759-B546-8E23-C7CF4CECE346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE19E94-ABD1-9E41-9FE2-C62D0A4C248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="215">
   <si>
     <t>Date</t>
   </si>
@@ -670,6 +670,15 @@
   </si>
   <si>
     <t>lessons/106b-using-LLM-to-learn.html</t>
+  </si>
+  <si>
+    <t>exercise</t>
+  </si>
+  <si>
+    <t>exercise_link</t>
+  </si>
+  <si>
+    <t>#task-1</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5054E2AF-B146-EF4C-9336-1C427A68EF7D}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.83203125" customWidth="1"/>
@@ -1054,10 +1063,10 @@
     <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
     <col min="4" max="5" width="28.1640625" customWidth="1"/>
     <col min="6" max="6" width="7" customWidth="1"/>
-    <col min="10" max="10" width="19.83203125" customWidth="1"/>
+    <col min="12" max="12" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
@@ -1083,19 +1092,25 @@
         <v>133</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1115,16 +1130,18 @@
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1144,22 +1161,22 @@
       <c r="F3" s="2">
         <v>1</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="J3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1179,22 +1196,22 @@
       <c r="F4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2</v>
       </c>
@@ -1214,24 +1231,24 @@
       <c r="F5" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2</v>
       </c>
@@ -1251,22 +1268,22 @@
       <c r="F6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2</v>
       </c>
@@ -1286,26 +1303,26 @@
       <c r="F7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -1331,8 +1348,10 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>3</v>
       </c>
@@ -1352,26 +1371,26 @@
       <c r="F9" s="2">
         <v>6</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>3</v>
       </c>
@@ -1391,22 +1410,22 @@
       <c r="F10" s="2">
         <v>7</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>3</v>
       </c>
@@ -1426,26 +1445,26 @@
       <c r="F11" s="2">
         <v>8</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>4</v>
       </c>
@@ -1471,8 +1490,10 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>4</v>
       </c>
@@ -1492,20 +1513,20 @@
       <c r="F13" s="2">
         <v>9</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>4</v>
       </c>
@@ -1519,14 +1540,14 @@
       <c r="D14" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="M14" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>4</v>
       </c>
@@ -1546,20 +1567,20 @@
       <c r="F15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>4</v>
       </c>
@@ -1579,12 +1600,12 @@
       <c r="F16" s="2">
         <v>11</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>5</v>
       </c>
@@ -1604,22 +1625,22 @@
       <c r="F17" s="2">
         <v>12</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>5</v>
       </c>
@@ -1639,22 +1660,22 @@
       <c r="F18" s="2">
         <v>13</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>5</v>
       </c>
@@ -1674,26 +1695,26 @@
       <c r="F19" s="2">
         <v>14</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="J19" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="K19" s="2" t="s">
+      <c r="M19" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>5</v>
       </c>
@@ -1713,22 +1734,22 @@
       <c r="F20" s="2">
         <v>15</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="J20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>5</v>
       </c>
@@ -1754,8 +1775,10 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>5</v>
       </c>
@@ -1781,8 +1804,10 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>6</v>
       </c>
@@ -1802,26 +1827,26 @@
       <c r="F23" s="2">
         <v>16</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="K23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>6</v>
       </c>
@@ -1841,22 +1866,22 @@
       <c r="F24" s="2">
         <v>17</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>6</v>
       </c>
@@ -1876,22 +1901,22 @@
       <c r="F25" s="2">
         <v>18</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>7</v>
       </c>
@@ -1913,8 +1938,10 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>8</v>
       </c>
@@ -1940,8 +1967,10 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>8</v>
       </c>
@@ -1961,22 +1990,22 @@
       <c r="F28" s="2">
         <v>19</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>8</v>
       </c>
@@ -1996,22 +2025,22 @@
       <c r="F29" s="2">
         <v>20</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>8</v>
       </c>
@@ -2031,26 +2060,26 @@
       <c r="F30" s="2">
         <v>21</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K30" s="2" t="s">
+      <c r="M30" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>8</v>
       </c>
@@ -2072,8 +2101,10 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>9</v>
       </c>
@@ -2095,12 +2126,14 @@
       <c r="H32" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>9</v>
       </c>
@@ -2118,12 +2151,14 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="4"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>10</v>
       </c>
@@ -2145,20 +2180,22 @@
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="I34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J34" s="2" t="s">
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>10</v>
       </c>
@@ -2178,22 +2215,22 @@
       <c r="F35" s="2">
         <v>23</v>
       </c>
-      <c r="G35" s="2" t="s">
+      <c r="I35" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L35" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>10</v>
       </c>
@@ -2213,22 +2250,22 @@
       <c r="F36" s="2">
         <v>24</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="I36" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>11</v>
       </c>
@@ -2248,26 +2285,26 @@
       <c r="F37" s="2">
         <v>25</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="I37" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L37" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K37" s="2" t="s">
+      <c r="M37" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>11</v>
       </c>
@@ -2289,16 +2326,18 @@
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J38" s="2" t="s">
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>11</v>
       </c>
@@ -2320,16 +2359,18 @@
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-      <c r="I39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J39" s="2" t="s">
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L39" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>11</v>
       </c>
@@ -2355,8 +2396,10 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>12</v>
       </c>
@@ -2376,26 +2419,26 @@
       <c r="F41" s="2">
         <v>28</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="I41" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="J41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J41" s="2" t="s">
+      <c r="K41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="K41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>12</v>
       </c>
@@ -2415,26 +2458,26 @@
       <c r="F42" s="2">
         <v>29</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="I42" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J42" s="2" t="s">
+      <c r="K42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>12</v>
       </c>
@@ -2454,22 +2497,22 @@
       <c r="F43" s="2">
         <v>30</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="I43" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="J43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>14</v>
       </c>
@@ -2495,8 +2538,10 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>13</v>
       </c>
@@ -2516,26 +2561,26 @@
       <c r="F45" s="2">
         <v>31</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="J45" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J45" s="2" t="s">
+      <c r="K45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>13</v>
       </c>
@@ -2555,26 +2600,26 @@
       <c r="F46" s="2">
         <v>32</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="I46" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="J46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J46" s="2" t="s">
+      <c r="K46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="K46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>13</v>
       </c>
@@ -2594,26 +2639,26 @@
       <c r="F47" s="2">
         <v>33</v>
       </c>
-      <c r="G47" s="2" t="s">
+      <c r="I47" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J47" s="2" t="s">
+      <c r="K47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="K47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>14</v>
       </c>
@@ -2635,16 +2680,18 @@
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="K48" s="2"/>
-      <c r="L48" s="2"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>14</v>
       </c>
@@ -2666,20 +2713,22 @@
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J49" s="2" t="s">
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="L49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>14</v>
       </c>
@@ -2701,16 +2750,18 @@
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="K50" s="2"/>
-      <c r="L50" s="2"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>14</v>
       </c>
@@ -2724,15 +2775,15 @@
       <c r="D51" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J51" s="2" t="s">
+      <c r="K51" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>202</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L51">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N51">
     <sortCondition ref="A2:A51"/>
     <sortCondition ref="B2:B51"/>
   </sortState>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE19E94-ABD1-9E41-9FE2-C62D0A4C248F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD723F6E-A7FC-254A-99BA-D411D08EA192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -1324,14 +1324,14 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="0"/>
-        <v>46038</v>
+        <v>46045</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>205</v>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD723F6E-A7FC-254A-99BA-D411D08EA192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7377D85A-F07A-CD43-B040-FFF1474105C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -1559,51 +1559,53 @@
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="F15" s="2">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>144</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="0"/>
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>210</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>211</v>
+        <v>94</v>
       </c>
       <c r="F16" s="2">
-        <v>11</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
@@ -1617,25 +1619,25 @@
         <v>46056</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F17" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1648,32 +1650,30 @@
         <v>2</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" si="0"/>
+        <f>DATEVALUE("2026-01-04")+B18+(A18-1)*7</f>
         <v>46056</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F18" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+        <v>144</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="2">

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7377D85A-F07A-CD43-B040-FFF1474105C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741D103F-7732-1644-9258-9777C025AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="218">
   <si>
     <t>Date</t>
   </si>
@@ -679,6 +679,15 @@
   </si>
   <si>
     <t>#task-1</t>
+  </si>
+  <si>
+    <t>11a-using-LLM-to-learn.html</t>
+  </si>
+  <si>
+    <t>Practice</t>
+  </si>
+  <si>
+    <t>#task-llm</t>
   </si>
 </sst>
 </file>
@@ -1567,10 +1576,18 @@
       <c r="F15" s="2">
         <v>11</v>
       </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="I15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="2">

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741D103F-7732-1644-9258-9777C025AD1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF481DE-9D17-F84C-8938-1864CE8EFBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="219">
   <si>
     <t>Date</t>
   </si>
@@ -688,6 +688,9 @@
   </si>
   <si>
     <t>#task-llm</t>
+  </si>
+  <si>
+    <t>10-facets</t>
   </si>
 </sst>
 </file>
@@ -1691,6 +1694,12 @@
       <c r="L18" s="2" t="s">
         <v>144</v>
       </c>
+      <c r="M18" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="2">

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFF481DE-9D17-F84C-8938-1864CE8EFBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B00CFE-E532-F74D-B84F-F0F4D92A1E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -246,9 +246,6 @@
     <t>Assignment 1 due</t>
   </si>
   <si>
-    <t>Assignment 2 due</t>
-  </si>
-  <si>
     <t>Assignment 3 due</t>
   </si>
   <si>
@@ -691,6 +688,9 @@
   </si>
   <si>
     <t>10-facets</t>
+  </si>
+  <si>
+    <t>Assignment 2 due (Feb 6 Munroe day)</t>
   </si>
 </sst>
 </file>
@@ -1089,25 +1089,25 @@
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="I1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>11</v>
@@ -1116,10 +1116,10 @@
         <v>9</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
@@ -1148,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1168,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -1177,13 +1177,13 @@
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1203,13 +1203,13 @@
         <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>12</v>
@@ -1218,7 +1218,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1238,26 +1238,26 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -1275,7 +1275,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" s="2">
         <v>4</v>
@@ -1290,7 +1290,7 @@
         <v>10</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -1310,13 +1310,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="2">
         <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>19</v>
@@ -1325,13 +1325,13 @@
         <v>10</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -1346,15 +1346,15 @@
         <v>46045</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1378,28 +1378,28 @@
         <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F9" s="2">
         <v>6</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -1417,13 +1417,13 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2">
         <v>7</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>39</v>
@@ -1432,7 +1432,7 @@
         <v>10</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1452,13 +1452,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F11" s="2">
         <v>8</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>40</v>
@@ -1467,13 +1467,13 @@
         <v>10</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -1493,10 +1493,10 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -1520,13 +1520,13 @@
         <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F13" s="2">
         <v>9</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>20</v>
@@ -1535,7 +1535,7 @@
         <v>10</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -1550,13 +1550,13 @@
         <v>46051</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -1571,25 +1571,25 @@
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="F15" s="2">
         <v>11</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="K15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1607,13 +1607,13 @@
         <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2">
         <v>12</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>42</v>
@@ -1622,7 +1622,7 @@
         <v>10</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -1642,13 +1642,13 @@
         <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2">
         <v>13</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>22</v>
@@ -1657,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1677,13 +1677,13 @@
         <v>27</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" s="2">
         <v>10</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>21</v>
@@ -1692,13 +1692,13 @@
         <v>10</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -1716,13 +1716,13 @@
         <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F19" s="2">
         <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
@@ -1731,13 +1731,13 @@
         <v>10</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -1755,13 +1755,13 @@
         <v>43</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F20" s="2">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -1770,32 +1770,32 @@
         <v>10</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B21" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="0"/>
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1821,10 +1821,10 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -1848,13 +1848,13 @@
         <v>28</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F23" s="2">
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>47</v>
@@ -1863,13 +1863,13 @@
         <v>10</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -1887,7 +1887,7 @@
         <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F24" s="2">
         <v>17</v>
@@ -1902,7 +1902,7 @@
         <v>10</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -1922,13 +1922,13 @@
         <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2">
         <v>18</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>49</v>
@@ -1937,7 +1937,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1954,7 +1954,7 @@
         <v>46069</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1979,15 +1979,15 @@
         <v>46076</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -2011,13 +2011,13 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2">
         <v>19</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>50</v>
@@ -2026,7 +2026,7 @@
         <v>10</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -2046,13 +2046,13 @@
         <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F29" s="2">
         <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>51</v>
@@ -2061,7 +2061,7 @@
         <v>10</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
@@ -2081,13 +2081,13 @@
         <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F30" s="2">
         <v>21</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>52</v>
@@ -2096,13 +2096,13 @@
         <v>10</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -2117,7 +2117,7 @@
         <v>46079</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2142,15 +2142,15 @@
         <v>46084</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -2171,7 +2171,7 @@
         <v>46086</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2199,7 +2199,7 @@
         <v>31</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F34" s="2">
         <v>22</v>
@@ -2212,13 +2212,13 @@
         <v>10</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
@@ -2236,7 +2236,7 @@
         <v>32</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F35" s="2">
         <v>23</v>
@@ -2251,7 +2251,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -2271,7 +2271,7 @@
         <v>33</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F36" s="2">
         <v>24</v>
@@ -2286,7 +2286,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
@@ -2306,28 +2306,28 @@
         <v>35</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F37" s="2">
         <v>25</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
@@ -2345,7 +2345,7 @@
         <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F38" s="2">
         <v>26</v>
@@ -2358,7 +2358,7 @@
         <v>10</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -2378,7 +2378,7 @@
         <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F39" s="2">
         <v>27</v>
@@ -2391,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -2408,15 +2408,15 @@
         <v>46101</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
@@ -2440,13 +2440,13 @@
         <v>36</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F41" s="2">
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>62</v>
@@ -2455,13 +2455,13 @@
         <v>10</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -2479,13 +2479,13 @@
         <v>56</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F42" s="2">
         <v>29</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>63</v>
@@ -2494,13 +2494,13 @@
         <v>10</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
@@ -2518,13 +2518,13 @@
         <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F43" s="2">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>64</v>
@@ -2533,7 +2533,7 @@
         <v>10</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -2550,15 +2550,15 @@
         <v>46118</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -2582,7 +2582,7 @@
         <v>55</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F45" s="2">
         <v>31</v>
@@ -2597,13 +2597,13 @@
         <v>10</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
@@ -2621,13 +2621,13 @@
         <v>54</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F46" s="2">
         <v>32</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>65</v>
@@ -2636,13 +2636,13 @@
         <v>10</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
@@ -2660,7 +2660,7 @@
         <v>37</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F47" s="2">
         <v>33</v>
@@ -2675,13 +2675,13 @@
         <v>10</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
@@ -2696,10 +2696,10 @@
         <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="F48" s="2">
         <v>34</v>
@@ -2712,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -2732,7 +2732,7 @@
         <v>38</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F49" s="2">
         <v>35</v>
@@ -2745,13 +2745,13 @@
         <v>10</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
@@ -2769,7 +2769,7 @@
         <v>59</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2">
         <v>36</v>
@@ -2782,7 +2782,7 @@
         <v>10</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -2799,13 +2799,13 @@
         <v>46119</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data-viz/schedule.xlsx
+++ b/data-viz/schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/airwin/git-repos/data-viz-course/data-viz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B00CFE-E532-F74D-B84F-F0F4D92A1E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8669C07-88C5-3749-B5A3-CA4C9D88D124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19400" xr2:uid="{D262D957-99A2-4240-BB5D-74EA57927089}"/>
   </bookViews>
@@ -621,9 +621,6 @@
     <t>13-tables</t>
   </si>
   <si>
-    <t>Task</t>
-  </si>
-  <si>
     <t>Other data formats</t>
   </si>
   <si>
@@ -691,6 +688,9 @@
   </si>
   <si>
     <t>Assignment 2 due (Feb 6 Munroe day)</t>
+  </si>
+  <si>
+    <t>Exercises</t>
   </si>
 </sst>
 </file>
@@ -1104,10 +1104,10 @@
         <v>132</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>11</v>
@@ -1177,7 +1177,7 @@
         <v>3</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>10</v>
@@ -1346,15 +1346,15 @@
         <v>46045</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -1571,25 +1571,25 @@
         <v>46051</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="F15" s="2">
         <v>11</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="K15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -1613,7 +1613,7 @@
         <v>12</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>42</v>
@@ -1698,7 +1698,7 @@
         <v>164</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -1761,7 +1761,7 @@
         <v>15</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>44</v>
@@ -1787,7 +1787,7 @@
         <v>46062</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
@@ -1824,7 +1824,7 @@
         <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
@@ -1854,7 +1854,7 @@
         <v>16</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>47</v>
@@ -2017,7 +2017,7 @@
         <v>19</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>50</v>
@@ -2052,7 +2052,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>51</v>
@@ -2117,7 +2117,7 @@
         <v>46079</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2142,7 +2142,7 @@
         <v>46084</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2171,7 +2171,7 @@
         <v>46086</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2446,7 +2446,7 @@
         <v>28</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>62</v>
@@ -2627,7 +2627,7 @@
         <v>32</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>65</v>
@@ -2696,10 +2696,10 @@
         <v>46119</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="F48" s="2">
         <v>34</v>
@@ -2712,7 +2712,7 @@
         <v>10</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -2745,7 +2745,7 @@
         <v>10</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>164</v>
@@ -2782,7 +2782,7 @@
         <v>10</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -2799,13 +2799,13 @@
         <v>46119</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
